--- a/tools/xlsform_samples/QOLIE-31.xlsx
+++ b/tools/xlsform_samples/QOLIE-31.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1718,28 +1718,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>QOLIE_31_scoring</t>
+          <t>QOLIE_31_overall_qol</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Computed Scores</t>
+          <t>overall_qol (mean_coded) - Overall QOL. Items 1, 14.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>(${q1} + ${q14}) div 2</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>QOLIE_31_overall_qol</t>
+          <t>QOLIE_31_emotional_wellbeing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>overall_qol (mean_coded) - Overall QOL. Items 1, 14.</t>
+          <t>emotional_wellbeing (mean_coded) - Emotional Well-Being. Items 3, 4, 5, 7, 9.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1766,7 +1766,7 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>(${q1} + ${q14}) div 2</t>
+          <t>(${q3} + ${q4} + ${q5} + ${q7} + ${q9}) div 5</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>QOLIE_31_emotional_wellbeing</t>
+          <t>QOLIE_31_energy_fatigue</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>emotional_wellbeing (mean_coded) - Emotional Well-Being. Items 3, 4, 5, 7, 9.</t>
+          <t>energy_fatigue (mean_coded) - Energy/Fatigue. Items 2, 6, 8, 10.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1796,7 +1796,7 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>(${q3} + ${q4} + ${q5} + ${q7} + ${q9}) div 5</t>
+          <t>(${q2} + ${q6} + ${q8} + ${q10}) div 4</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -1813,12 +1813,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>QOLIE_31_energy_fatigue</t>
+          <t>QOLIE_31_seizure_worry</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>energy_fatigue (mean_coded) - Energy/Fatigue. Items 2, 6, 8, 10.</t>
+          <t>seizure_worry (mean_coded) - Seizure Worry. Items 11, 21, 22, 23, 24.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1826,7 +1826,7 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>(${q2} + ${q6} + ${q8} + ${q10}) div 4</t>
+          <t>(${q11} + ${q21} + ${q22} + ${q23} + ${q24}) div 5</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -1843,12 +1843,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>QOLIE_31_seizure_worry</t>
+          <t>QOLIE_31_cognitive</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>seizure_worry (mean_coded) - Seizure Worry. Items 11, 21, 22, 23, 24.</t>
+          <t>cognitive (mean_coded) - Cognitive Functioning. Items 12, 15, 16, 17, 18, 26.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1856,7 +1856,7 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>(${q11} + ${q21} + ${q22} + ${q23} + ${q24}) div 5</t>
+          <t>(${q12} + ${q15} + ${q16} + ${q17} + ${q18} + ${q26}) div 6</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>QOLIE_31_cognitive</t>
+          <t>QOLIE_31_medication_effects</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>cognitive (mean_coded) - Cognitive Functioning. Items 12, 15, 16, 17, 18, 26.</t>
+          <t>medication_effects (mean_coded) - Medication Effects. Items 24, 29, 30.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1886,7 +1886,7 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>(${q12} + ${q15} + ${q16} + ${q17} + ${q18} + ${q26}) div 6</t>
+          <t>(${q24} + ${q29} + ${q30}) div 3</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>QOLIE_31_medication_effects</t>
+          <t>QOLIE_31_social_function</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>medication_effects (mean_coded) - Medication Effects. Items 24, 29, 30.</t>
+          <t>social_function (mean_coded) - Social Functioning. Items 13, 19, 20, 27, 28.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1916,7 +1916,7 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>(${q24} + ${q29} + ${q30}) div 3</t>
+          <t>(${q13} + ${q19} + ${q20} + ${q27} + ${q28}) div 5</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -1924,58 +1924,6 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>QOLIE_31_social_function</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>social_function (mean_coded) - Social Functioning. Items 13, 19, 20, 27, 28.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>(${q13} + ${q19} + ${q20} + ${q27} + ${q28}) div 5</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>QOLIE_31_scoring</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/xlsform_samples/QOLIE-31.xlsx
+++ b/tools/xlsform_samples/QOLIE-31.xlsx
@@ -2716,7 +2716,11 @@
           <t>20260618</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>English (en)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
